--- a/output/optimized_schedule.xlsx
+++ b/output/optimized_schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/p_moosavi_rotman_utoronto_ca/Documents/Conferences/CORS 2026/OR Challenge/Proposed Framework Code/FIFA2026CORS/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_2CF1148E90C59F5373183911595ED87656CD34F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28AE95C2-45D0-4628-9C22-0D24C59C6931}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_6DFD149E90159A3E23992A11595ED87656CD5471" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F03CAADC-F4A0-434F-946A-3F7153A2C70A}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="97">
   <si>
     <t>match_id</t>
   </si>
@@ -55,301 +55,262 @@
     <t>RSA</t>
   </si>
   <si>
-    <t>BOS</t>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>KOR</t>
+  </si>
+  <si>
+    <t>CZE</t>
+  </si>
+  <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>BIH</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>PAR</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>AUS</t>
+  </si>
+  <si>
+    <t>TUR</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>QAT</t>
+  </si>
+  <si>
+    <t>SUI</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>BRA</t>
+  </si>
+  <si>
+    <t>MAR</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
+  </si>
+  <si>
+    <t>HAI</t>
+  </si>
+  <si>
+    <t>SCO</t>
+  </si>
+  <si>
+    <t>VAN</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>GER</t>
+  </si>
+  <si>
+    <t>CUW</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>NED</t>
+  </si>
+  <si>
+    <t>JPN</t>
+  </si>
+  <si>
+    <t>CIV</t>
+  </si>
+  <si>
+    <t>ECU</t>
+  </si>
+  <si>
+    <t>2026-06-17</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>SWE</t>
+  </si>
+  <si>
+    <t>TUN</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>EGY</t>
+  </si>
+  <si>
+    <t>KSA</t>
+  </si>
+  <si>
+    <t>URU</t>
   </si>
   <si>
     <t>2026-06-23</t>
   </si>
   <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>KOR</t>
-  </si>
-  <si>
-    <t>CZE</t>
-  </si>
-  <si>
-    <t>SFO</t>
+    <t>IRN</t>
+  </si>
+  <si>
+    <t>NZL</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>FRA</t>
+  </si>
+  <si>
+    <t>SEN</t>
+  </si>
+  <si>
+    <t>IRQ</t>
+  </si>
+  <si>
+    <t>NOR</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>ARG</t>
+  </si>
+  <si>
+    <t>ALG</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>JOR</t>
+  </si>
+  <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>POR</t>
+  </si>
+  <si>
+    <t>COD</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>CRO</t>
   </si>
   <si>
     <t>2026-06-22</t>
   </si>
   <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>BIH</t>
-  </si>
-  <si>
-    <t>ATL</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>PAR</t>
-  </si>
-  <si>
-    <t>MTY</t>
+    <t>GHA</t>
+  </si>
+  <si>
+    <t>PAN</t>
   </si>
   <si>
     <t>2026-06-20</t>
   </si>
   <si>
-    <t>AUS</t>
-  </si>
-  <si>
-    <t>TUR</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>QAT</t>
-  </si>
-  <si>
-    <t>SUI</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>BRA</t>
-  </si>
-  <si>
-    <t>MAR</t>
-  </si>
-  <si>
-    <t>DAL</t>
+    <t>UZB</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
   </si>
   <si>
     <t>13:00</t>
   </si>
   <si>
-    <t>HAI</t>
-  </si>
-  <si>
-    <t>SCO</t>
-  </si>
-  <si>
-    <t>TOR</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>GER</t>
-  </si>
-  <si>
-    <t>CUW</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>NED</t>
-  </si>
-  <si>
-    <t>JPN</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>CIV</t>
-  </si>
-  <si>
-    <t>ECU</t>
-  </si>
-  <si>
-    <t>LAX</t>
-  </si>
-  <si>
-    <t>2026-06-16</t>
-  </si>
-  <si>
     <t>19:00</t>
   </si>
   <si>
-    <t>SWE</t>
-  </si>
-  <si>
-    <t>TUN</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>ESP</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>EGY</t>
-  </si>
-  <si>
-    <t>SEA</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>KSA</t>
-  </si>
-  <si>
-    <t>URU</t>
-  </si>
-  <si>
-    <t>HOU</t>
-  </si>
-  <si>
-    <t>IRN</t>
-  </si>
-  <si>
-    <t>NZL</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>FRA</t>
-  </si>
-  <si>
-    <t>SEN</t>
-  </si>
-  <si>
-    <t>IRQ</t>
-  </si>
-  <si>
-    <t>NOR</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>ARG</t>
-  </si>
-  <si>
-    <t>ALG</t>
-  </si>
-  <si>
-    <t>VAN</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>JOR</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>POR</t>
-  </si>
-  <si>
-    <t>COD</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>CRO</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>GHA</t>
-  </si>
-  <si>
-    <t>PAN</t>
-  </si>
-  <si>
-    <t>NYC</t>
-  </si>
-  <si>
-    <t>UZB</t>
-  </si>
-  <si>
-    <t>COL</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>GDL</t>
-  </si>
-  <si>
-    <t>2026-06-27</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
     <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>KC</t>
   </si>
 </sst>
 </file>
@@ -394,9 +355,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -415,7 +374,51 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -426,6 +429,29 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{87C2040E-0C8C-4720-B3A7-473697B3369D}" name="Table1" displayName="Table1" ref="A1:H73" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A1:H73" xr:uid="{87C2040E-0C8C-4720-B3A7-473697B3369D}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="J"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{B1F8A6C4-A27E-46F7-AAEC-1374BA8CF905}" name="match_id"/>
+    <tableColumn id="2" xr3:uid="{0B1AE186-7293-4AC8-AD00-354B208AF133}" name="group"/>
+    <tableColumn id="3" xr3:uid="{0D27D639-DA38-4486-B3C7-EF4FFA8DCF5F}" name="round"/>
+    <tableColumn id="4" xr3:uid="{987099F0-BFE9-4CAB-BC40-CFF99684EE0D}" name="team_a_id"/>
+    <tableColumn id="5" xr3:uid="{AB0628A5-41A2-437B-BF3F-BEF00435F0B7}" name="team_b_id"/>
+    <tableColumn id="6" xr3:uid="{BE204525-CCBA-4A9C-AFC0-66FB2997727C}" name="venue_id"/>
+    <tableColumn id="7" xr3:uid="{8B9538D8-5333-4E2B-90E3-A16300200737}" name="date"/>
+    <tableColumn id="8" xr3:uid="{6B26CABD-C59B-44D6-855B-0E21A6790FE1}" name="kickoff_local"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -716,8 +742,12 @@
   <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="1" max="1" width="10.1328125" customWidth="1"/>
+    <col min="4" max="4" width="11.1328125" customWidth="1"/>
+    <col min="5" max="5" width="11.265625" customWidth="1"/>
+    <col min="6" max="6" width="10.1328125" customWidth="1"/>
     <col min="7" max="7" width="9.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -746,7 +776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
@@ -763,16 +793,16 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
@@ -783,435 +813,435 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
       <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
       <c r="H4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H12" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="H15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="H17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E19" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F19" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="H19" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
@@ -1219,25 +1249,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="G20" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="H20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
@@ -1245,132 +1275,132 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="F22" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F24" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1381,48 +1411,48 @@
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="H26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="H27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1436,354 +1466,354 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H29" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s">
         <v>26</v>
       </c>
-      <c r="E30" t="s">
-        <v>30</v>
-      </c>
       <c r="F30" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30" t="s">
         <v>44</v>
       </c>
-      <c r="G30" t="s">
-        <v>29</v>
-      </c>
-      <c r="H30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E31" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F31" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s">
         <v>16</v>
       </c>
-      <c r="G31" t="s">
-        <v>104</v>
-      </c>
       <c r="H31" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E32" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" t="s">
         <v>38</v>
       </c>
-      <c r="E32" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" t="s">
-        <v>71</v>
-      </c>
       <c r="G32" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E34" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F34" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E35" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F35" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G35" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F36" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C37">
         <v>2</v>
       </c>
       <c r="D37" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E37" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F37" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H37" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
       <c r="D38" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E38" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F38" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E39" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="F39" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G39" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F40" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="G40" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="H40" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E41" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F41" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="H41" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.45">
@@ -1791,77 +1821,77 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C42">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E42" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F42" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="H42" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E43" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F43" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="H43" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E44" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F44" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.45">
@@ -1869,236 +1899,236 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" t="s">
+        <v>77</v>
+      </c>
+      <c r="E45" t="s">
+        <v>75</v>
+      </c>
+      <c r="F45" t="s">
+        <v>9</v>
+      </c>
+      <c r="G45" t="s">
         <v>90</v>
       </c>
-      <c r="E45" t="s">
-        <v>86</v>
-      </c>
-      <c r="F45" t="s">
-        <v>87</v>
-      </c>
-      <c r="G45" t="s">
-        <v>104</v>
-      </c>
       <c r="H45" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="E46" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F46" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="H46" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C47">
         <v>2</v>
       </c>
       <c r="D47" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E47" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F47" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>108</v>
+        <v>11</v>
       </c>
       <c r="H47" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C48">
         <v>2</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E48" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="F48" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="H48" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E49" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="F49" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="H49" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E50" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F50" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="H50" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E51" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F51" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C52">
         <v>3</v>
       </c>
       <c r="D52" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E52" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F52" t="s">
         <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="H52" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="H53" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2109,22 +2139,22 @@
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
       </c>
       <c r="F54" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="H54" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2138,432 +2168,432 @@
         <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F55" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="G55" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E56" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F56" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H56" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C57">
         <v>3</v>
       </c>
       <c r="D57" t="s">
+        <v>43</v>
+      </c>
+      <c r="E57" t="s">
         <v>48</v>
       </c>
-      <c r="E57" t="s">
-        <v>56</v>
-      </c>
       <c r="F57" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="H57" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C58">
         <v>3</v>
       </c>
       <c r="D58" t="s">
+        <v>47</v>
+      </c>
+      <c r="E58" t="s">
         <v>52</v>
       </c>
-      <c r="E58" t="s">
-        <v>61</v>
-      </c>
       <c r="F58" t="s">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="H58" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E59" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F59" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="G59" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E60" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F60" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="H61" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C62">
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E62" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="H62" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C63">
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E63" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F63" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G63" t="s">
+        <v>66</v>
+      </c>
+      <c r="H63" t="s">
         <v>54</v>
       </c>
-      <c r="H63" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E64" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F64" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="G64" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E65" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F65" t="s">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H65" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E66" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="F66" t="s">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="G66" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="H66" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E67" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F67" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E68" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F68" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H68" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E69" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F69" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="H69" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E70" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F70" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E71" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F71" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="H71" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.45">
@@ -2571,25 +2601,25 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C72">
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E72" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="F72" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="G72" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="H72" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.45">
@@ -2597,34 +2627,31 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E73" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F73" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="H73" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{78aac226-2f03-4b4d-9037-b46d56c55210}" enabled="0" method="" siteId="{78aac226-2f03-4b4d-9037-b46d56c55210}" removed="1"/>
-</clbl:labelList>
 </file>